--- a/docs/07_CWE_Coverage/verification_evidence_matrix.xlsx
+++ b/docs/07_CWE_Coverage/verification_evidence_matrix.xlsx
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2f6c9db41c36d472a21bd770cc230dd3fa30bd125ecbf310016dd97af624e2b2</t>
+          <t>5143f2411e505d59f265e0de2d267e3a10a746643c8bbf563c711c984da8d49c</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>FILE_NOT_FOUND</t>
+          <t>dfbbbb98a65e43f43beaac7bd1de27fcd247e661e8eedd29167b2ae9c3ec0497</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>FILE_NOT_FOUND</t>
+          <t>ede15569857acf940b67a5427dbeb6303a36323f679786b8531f724239448bf0</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>56d981bdf5319f2bbc2e1dec5d2a98fc85d6ffe63df15e9d9dedd69385a3bbf0</t>
+          <t>6a11e46767b0f5735f570535b6a554317c516a6ebad8687f3c49ee718721b653</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2f0c3daadf55765aa334afea68879b25ee13f939e249c343734a590e21848582</t>
+          <t>cae882d1762aeae07479161e3e9de25f82b86cd004dbbae09cc7669e6b70f3a8</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2085aa0ba93e906791890349350237d3d218e51ce3a3fa92ea0776512d833d27</t>
+          <t>edf96458c731f745615923155be5df14d5b1657932862be00971c87a7ee9fb3b</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
